--- a/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
@@ -471,10 +471,10 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>22</v>
@@ -483,7 +483,7 @@
         <v>70.97</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -591,7 +591,7 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>22</v>
@@ -708,7 +708,7 @@
         <v>70.97</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,24 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>GROT</t>
+  </si>
+  <si>
+    <t>AZURA</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
   </si>
 </sst>
 </file>
@@ -770,7 +788,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -800,6 +818,52 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920230</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920251</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
@@ -512,7 +512,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -521,10 +521,10 @@
         <v>8</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>80.48999999999999</v>
+        <v>80</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -626,13 +626,13 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -737,7 +737,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>8</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>80.48999999999999</v>
+        <v>80</v>
       </c>
       <c r="H3">
         <v>7</v>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -73,19 +73,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
     <t>GROT</t>
-  </si>
-  <si>
-    <t>AZURA</t>
   </si>
   <si>
     <t>DANIELA DEL CARMEN</t>
@@ -538,10 +529,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -550,7 +541,7 @@
         <v>28</v>
       </c>
       <c r="G4">
-        <v>87.5</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H4">
         <v>7.3</v>
@@ -649,10 +640,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>32</v>
@@ -763,10 +754,10 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -775,7 +766,7 @@
         <v>28</v>
       </c>
       <c r="G4">
-        <v>87.5</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H4">
         <v>7.3</v>
@@ -788,7 +779,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -820,16 +811,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920230</v>
+        <v>22330051920251</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -839,29 +830,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920251</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -76,10 +76,19 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>GROT</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>KEVIN RAUL</t>
   </si>
 </sst>
 </file>
@@ -779,7 +788,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -817,10 +826,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -829,6 +838,29 @@
         <v>10</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920425</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -73,22 +73,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>RIVERA</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
   </si>
   <si>
     <t>GROT</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>AMALIA PAULINA</t>
   </si>
   <si>
     <t>DANIELA DEL CARMEN</t>
   </si>
   <si>
-    <t>KEVIN RAUL</t>
+    <t>NORMA ANGELICA</t>
   </si>
 </sst>
 </file>
@@ -541,16 +550,16 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>84.84999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H4">
         <v>7.3</v>
@@ -606,16 +615,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>58.06</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -629,16 +641,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>77.5</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -652,16 +667,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>87.88</v>
+      </c>
+      <c r="H4">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -717,16 +735,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>70.97</v>
+        <v>58.06</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -743,16 +761,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -766,19 +784,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>84.84999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -788,7 +806,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -820,16 +838,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920251</v>
+        <v>22330051920240</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -843,25 +861,48 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920425</v>
+        <v>22330051920251</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330061460548</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -73,31 +73,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>GROT</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>NORMA ANGELICA</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>HECTOR ALAN</t>
+  </si>
+  <si>
+    <t>ARACELI</t>
   </si>
 </sst>
 </file>
@@ -735,16 +726,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>58.06</v>
+        <v>61.29</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -761,16 +752,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>77.5</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -796,7 +787,7 @@
         <v>87.88</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -806,7 +797,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -838,39 +829,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920240</v>
+        <v>22330051920187</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920251</v>
+        <v>22330051920318</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -879,29 +870,6 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330061460548</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -73,22 +73,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>PORTILLA</t>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>ARACELI</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>BRENDA JANELY</t>
   </si>
   <si>
     <t>HECTOR ALAN</t>
-  </si>
-  <si>
-    <t>ARACELI</t>
   </si>
 </sst>
 </file>
@@ -797,7 +824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -829,16 +856,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920187</v>
+        <v>22330051920193</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -847,7 +874,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -858,10 +885,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -870,6 +897,75 @@
         <v>10</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920366</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920259</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920187</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="54">
   <si>
     <t>Mat</t>
   </si>
@@ -73,49 +73,112 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>ARACELI</t>
+  </si>
+  <si>
+    <t>NOEMI DEL ROCIO</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>BRENDA JANELY</t>
+  </si>
+  <si>
+    <t>HECTOR ALAN</t>
   </si>
   <si>
     <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>ARACELI</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>BRENDA JANELY</t>
-  </si>
-  <si>
-    <t>HECTOR ALAN</t>
   </si>
 </sst>
 </file>
@@ -824,7 +887,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -856,16 +919,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920193</v>
+        <v>22330051920413</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -879,22 +942,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920318</v>
+        <v>22330051920356</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -902,16 +965,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920366</v>
+        <v>22330051920233</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -925,16 +988,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920259</v>
+        <v>22330051920236</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -948,24 +1011,185 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920187</v>
+        <v>22330051920237</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920369</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920318</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920253</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920366</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920259</v>
+      </c>
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920187</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
         <v>9</v>
       </c>
-      <c r="G6">
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920193</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
     </row>
